--- a/光伏配储项目/电价数据/2026/保城站.xlsx
+++ b/光伏配储项目/电价数据/2026/保城站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50893</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.72709</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57108</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.57155</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.49833</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49182</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43741</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43382</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42243</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42293</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41682</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42053</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41379</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44323</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27902</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11304</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09234999999999999</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.09919</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08291</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.10858</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03765</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.07851999999999999</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.09045</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.09772</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.08537</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08957999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07435</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.03555</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.02008</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14369</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21316</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22624</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25271</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.20391</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.0614</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00688</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.26503</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.12711</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.26079</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26173</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.25763</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.17395</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.25923</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.50718</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.44541</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.72412</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.5883999999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42485</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43969</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41929</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56709</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44307</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.59461</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.76795</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63618</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.59785</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7143699999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.80414</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41443</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6436499999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.57828</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.6293800000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.51348</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.47917</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.60582</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.58217</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46327</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48039</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4168</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42669</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.2952</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.68975</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.8375199999999999</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7414500000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5036</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5139900000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50324</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49601</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47987</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4659700000000001</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.48737</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55996</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.57855</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42521</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5032300000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.14532</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.26711</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.04654999999999999</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.76886</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.89055</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.68336</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.47258</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.12231</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.28479</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.46827</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.24097</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.17994</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.18852</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.23864</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.5629</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.44031</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6283200000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.61803</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.65099</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.42596</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.44606</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.62752</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43286</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.51952</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43552</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3351</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50944</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38981</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42918</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44489</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47393</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43955</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.24712</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25157</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.23588</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.1911</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.22888</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27298</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47517</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5216799999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48159</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.14879</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.25163</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.28284</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.44249</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39104</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43183</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.5042</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5021100000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5882200000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5007</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.58802</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.4553</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.42705</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.44649</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43304</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34102</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.46414</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.49569</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.47314</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.50856</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.44482</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.5410900000000001</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.55284</v>
+      </c>
+      <c r="M120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.42058</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.00409</v>
+      </c>
+      <c r="P120" t="n">
+        <v>-0.03331</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.05838</v>
+      </c>
+      <c r="S120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.04821</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.08913</v>
+      </c>
+      <c r="V120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.008869999999999999</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.01378</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.04503</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.03138</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.00644</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.12593</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>-0.02515</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.25953</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.07576000000000001</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.04778</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>-0.04843</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.17707</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>-0.03912</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.05619</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.02302</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.05604</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>-0.04877</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.13664</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.14186</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.09794</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>-0.00783</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>-0.02959</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.13952</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.07165000000000001</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.08376</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.23732</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29765</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.25418</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.24232</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.16416</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.22534</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.14367</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26148</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.03939</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04996</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04017</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04596</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.05525</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.05213</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.05627</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.00827</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04292</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.03881</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.02879</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.02493</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.02525</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.02737</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.02612</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.02209</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.02871</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.03834000000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.02968</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.02731</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.02978</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.03139</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04069</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.03044</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04090999999999999</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21949</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.05534</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.06961000000000001</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06642000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00287</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14521</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03548</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09744</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40195</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41108</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46784</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41802</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35131</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65962</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44801</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42512</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04332</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04729999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04626</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04661</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04661</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04661</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04601</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04462</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.0195</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04116</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10935</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00066</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03073</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.03629</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04208</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04469</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04627000000000001</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.0462</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04449</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04418</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04608</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04419</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03870000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04586</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03691</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.03875</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04778</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04874</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19853</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14187</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26766</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33474</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31471</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40376</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28714</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27031</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.26987</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17168</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15791</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17016</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14708</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15883</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23498</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21331</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22573</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26785</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.2846</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.27939</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.26947</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28005</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42954</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46258</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42058</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15651</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076499999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62202</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49795</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92035</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49453</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.90807</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.84451</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.28596</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.86913</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6283200000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.16898</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8596200000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.52518</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.31236</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.02017</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5123099999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.77537</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5316799999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.75724</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7651</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8748400000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.86566</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.47848</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.38092</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.43313</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.18803</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8781100000000001</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5505800000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.60305</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5335800000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4922</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45341</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42194</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43373</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44893</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45232</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41858</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5861900000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5959099999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6025700000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.47449</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46672</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5855</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45128</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88163</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6238899999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.84576</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.82521</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86003</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44103</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.43093</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26777</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41108</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45379</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41612</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3538</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.89498</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.45857</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41087</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50186</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38856</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.1643</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26197</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19812</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27735</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.17111</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25566</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27691</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.6727000000000001</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42329</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42132</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5996699999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8910399999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33624</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.20132</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6969</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78669</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.70325</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58163</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45312</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45111</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50144</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43876</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50285</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.4143</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43489</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42969</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45235</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43583</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41349</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42523</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48086</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.54327</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24974</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16098</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.25801</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.26723</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.04305</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25046</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.27777</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.25806</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40291</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5566</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46265</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.0829</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.4653</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32355</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42265</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29608</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22597</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14094</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14585</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28169</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15389</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14317</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13823</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14207</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13724</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24834</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13741</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25689</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13636</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.09994</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10817</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10819</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12772</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13632</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14071</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27838</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.47791</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43962</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44374</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44329</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40133</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34842</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5369299999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46894</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42347</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28426</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2789700000000001</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19728</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25013</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24782</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40277</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25186</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.27237</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36041</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43723</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42958</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25122</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.25669</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.08419</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.21956</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25953</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27762</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37343</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.40925</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6574800000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.4982799999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.13063</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28127</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28448</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.41648</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.41336</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35005</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.23963</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43799</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65915</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.74662</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.44562</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.20994</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45796</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34506</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26576</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14815</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28643</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19806</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25874</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27861</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27964</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.20577</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.22912</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27231</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28528</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.27855</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.15447</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.2575</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43625</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.43487</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6540199999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.61539</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.62409</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.54711</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.16068</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.4899</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.82698</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.48282</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5257999999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48438</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43163</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36055</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48824</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5225700000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47816</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48244</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41562</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4075299999999999</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39486</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40105</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41418</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45297</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45156</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56504</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45307</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.53008</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44756</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44268</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44239</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42754</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4358399999999999</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40195</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.61991</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.17751</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.27392</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43613</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49353</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44021</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.52523</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.52411</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5508999999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.7039299999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.73302</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.91287</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.78838</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.81838</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5832999999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5277500000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83688</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7686499999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62151</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6709700000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.46932</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48214</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47629</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46955</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55047</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42627</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44152</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45519</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45491</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18784</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38309</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4665899999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47603</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10003</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18569</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42196</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.44315</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42198</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.4218</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36844</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44651</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39352</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.26512</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22596</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22596</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27743</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24466</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.22109</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14486</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27574</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.23607</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.24723</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.24903</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16515</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.19762</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27038</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24502</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.28004</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26062</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24217</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34956</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01787</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03985</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04986</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04729</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04645000000000001</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>-0.04897</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>-0.04596</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.04623</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.22791</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>-0.04955</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25258</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27268</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32227</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.28135</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25912</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.26159</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.04398</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.18724</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.47835</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.51319</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-0.02724</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>-0.04635</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.40773</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43995</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14196</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27294</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26987</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.25126</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>-0.04515</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29144</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>-0.01595</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32832</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.21144</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.2498</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="O139" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.50185</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50208</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.38827</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.47328</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25163</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.26942</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.45338</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46379</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.50915</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.28468</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.15514</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45968</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36896</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47771</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40127</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.41872</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26101</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29361</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42271</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49387</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.57269</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5650599999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.52647</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.59578</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49413</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5311900000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.44464</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5867599999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.65813</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.66254</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54277</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.54235</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37147</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.09115999999999999</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.14962</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.23898</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.07562000000000001</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.20977</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.22669</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.05579</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.20248</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.17599</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.02527</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.17575</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.13643</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.12882</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.09140999999999999</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.10842</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.13948</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>-0.01432</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.24616</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.27062</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>-0.01562</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>-0.03946</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.01386</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.01907</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06468</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13092</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02882</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.10029</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.13861</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00204</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.25446</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26197</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.13642</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06218</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05276</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.05713</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-0.02374</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.04499</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06015</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.00924</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>-0.01151</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>-0.04431</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>-0.03204</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.00872</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.22677</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.0727</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.42364</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40377</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.07736</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.12976</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41397</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.11212</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>-0.0269</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40858</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.12447</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.09995</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.08427</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.08638</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>-0.01854</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.06748</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="E142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="I142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K142" t="n">
+        <v>-0.01571</v>
+      </c>
+      <c r="L142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.00507</v>
+      </c>
+      <c r="P142" t="n">
+        <v>-0.03722</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>-0.01688</v>
+      </c>
+      <c r="R142" t="n">
+        <v>-0.01142</v>
+      </c>
+      <c r="S142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U142" t="n">
+        <v>-0.03352</v>
+      </c>
+      <c r="V142" t="n">
+        <v>-0.04203</v>
+      </c>
+      <c r="W142" t="n">
+        <v>-0.0228</v>
+      </c>
+      <c r="X142" t="n">
+        <v>-0.01889</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.009269999999999999</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>-0.01918</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>-0.04192</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>-0.00484</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>-0.02517</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>-0.04668</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01211</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01011</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.02447</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.02711</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.01365</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01652</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.03028</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.009269999999999999</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.00039</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.00106</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15341</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.0313</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.03527</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>-0.02403</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.01487</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.12408</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>-0.02772</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>-0.01283</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>-0.01637</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.06159000000000001</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>-0.03743</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41128</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40828</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.22463</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.18667</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.18437</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.08706</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.01581</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.10409</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.02806</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.09165000000000001</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.10915</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.09011</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.13152</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.10128</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.08128000000000001</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.09295</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.04641</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.0945</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.23824</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.01304</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.02603</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="G143" t="n">
+        <v>-0.00508</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-0.02644</v>
+      </c>
+      <c r="I143" t="n">
+        <v>-0.00333</v>
+      </c>
+      <c r="J143" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="K143" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="L143" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="M143" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="N143" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="O143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>-0.04982</v>
+      </c>
+      <c r="R143" t="n">
+        <v>-0.01951</v>
+      </c>
+      <c r="S143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T143" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="U143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>-0.03841</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>-0.01742</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>-0.04014</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.02076</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.07887000000000001</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04899</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04758</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03988000000000001</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.03351</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.03965999999999999</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.04903</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02152</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.01666</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.06899</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.008330000000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>-0.04061</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.06615</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.25547</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.13655</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.02679</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>-0.04015999999999999</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.03917</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.11375</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.13167</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.20519</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.12135</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.11916</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.10917</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.12268</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.10163</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.11043</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.11836</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>-0.01005</v>
       </c>
     </row>
   </sheetData>
